--- a/Experimental_Data.xlsx
+++ b/Experimental_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252E2C00-DC38-4ED4-ABDC-3C07B806749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E94FBBB-D5DC-436F-AF67-4D40309C241E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table7_Solution_Performance" sheetId="2" r:id="rId1"/>
@@ -67,10 +67,10 @@
     <t>A</t>
   </si>
   <si>
-    <t>Rollout</t>
-  </si>
-  <si>
-    <t>Q-Learning</t>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>Q-learning</t>
   </si>
   <si>
     <t>B</t>
@@ -85,13 +85,13 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>Unassigned</t>
+    <t>Not started</t>
   </si>
   <si>
     <t>In progress</t>
   </si>
   <si>
-    <t>Rollout N</t>
+    <t>ADP N</t>
   </si>
   <si>
     <t>QL episodes</t>
@@ -100,16 +100,16 @@
     <t>Interpretation</t>
   </si>
   <si>
-    <t>Rollout mean cost</t>
+    <t>ADP mean cost</t>
   </si>
   <si>
     <t>QL mean cost</t>
   </si>
   <si>
-    <t>Q-Learning cheaper</t>
-  </si>
-  <si>
-    <t>Rollout cheaper</t>
+    <t>Q-learning cheaper</t>
+  </si>
+  <si>
+    <t>ADP cheaper</t>
   </si>
   <si>
     <t>K</t>
@@ -130,7 +130,7 @@
     <t>Instance</t>
   </si>
   <si>
-    <t>Rollout cost</t>
+    <t>ADP cost</t>
   </si>
   <si>
     <t>QL cost</t>
@@ -946,13 +946,13 @@
         <v>87416</v>
       </c>
       <c r="F14" s="3">
-        <v>8.0400000000000003E-5</v>
+        <v>8.8739999999999994E-5</v>
       </c>
       <c r="G14" s="3">
-        <v>0.60399999999999998</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="H14" s="3">
-        <v>102.4</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
@@ -998,13 +998,13 @@
         <v>90202</v>
       </c>
       <c r="F16" s="3">
-        <v>8.1810000000000004E-5</v>
+        <v>9.0099999999999995E-5</v>
       </c>
       <c r="G16" s="3">
-        <v>0.61199999999999999</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="H16" s="3">
-        <v>95.1</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
@@ -1050,13 +1050,13 @@
         <v>90938</v>
       </c>
       <c r="F18" s="3">
-        <v>7.7550000000000001E-5</v>
+        <v>9.0279999999999996E-5</v>
       </c>
       <c r="G18" s="3">
-        <v>0.61399999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H18" s="3">
-        <v>99.7</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
@@ -1669,11 +1669,11 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.15">
@@ -2556,10 +2556,10 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
